--- a/templates/日报模板.xlsx
+++ b/templates/日报模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\idea-workspase-skills\daily-merge\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7C993D-9B46-4B7C-BA87-72F49F4C1CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF1A05E-F065-46C3-AB86-ABBA67A6827E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1656" yWindow="0" windowWidth="34128" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10224" yWindow="576" windowWidth="29280" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="胡志伟" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>实际完成时间</t>
   </si>
@@ -122,11 +122,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>*序号
-（全局唯一）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>*任务描述</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -181,6 +176,31 @@
   <si>
     <t xml:space="preserve">*预计工作人时
 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>*序号
+（每一个任务编号全局唯一）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>8、开会和沟通也当作任务记录时常</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、每个月第一天重新用干净的模板文件，上个月未完成的任务连同原有序号记得先复制进来 再继续记录。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>10、序号（全局唯一） ---》 修改一下，是每个任务同一个序号全局唯一，也就是说某个任务工作了多天，每天的copy记录里序号保持跟之前一致。</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>11、实际工作人时：某个任务第一天花费了2小时，进度50%，当天填写实际工作人时【2】不填写实际完成时间，第二天这个任务又花了3小时，进度100%，当天填写实际工作人时【5】今天的3+昨天的2，填写实际完成时间为当天时间.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>12、当天未完成的任务，第二天记得要copy一下，哪怕第二天也没时间做。这样方便调整每位同学手上的任务，可以做一些平衡。</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -191,7 +211,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
@@ -245,6 +265,21 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -270,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -306,25 +341,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -375,6 +419,21 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -631,289 +690,409 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A49D6851-1A1C-4785-819D-8FAD6FAF2B3F}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="78">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" ht="81">
+      <c r="A1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="E1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="10" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="10"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="10"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="10"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="10"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="10"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="10"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="10"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="10"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="1"/>
       <c r="E10" s="1"/>
-      <c r="H10" s="5"/>
-      <c r="K10" s="5"/>
+      <c r="H10" s="3"/>
+      <c r="K10" s="3"/>
       <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="1"/>
       <c r="E11" s="1"/>
-      <c r="H11" s="5"/>
-      <c r="K11" s="5"/>
+      <c r="H11" s="3"/>
+      <c r="K11" s="3"/>
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="H12" s="5"/>
-      <c r="K12" s="5"/>
+      <c r="H12" s="3"/>
+      <c r="K12" s="3"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:14" ht="62.4">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:14">
+      <c r="A13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="1"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="21"/>
+      <c r="B14" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="1"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="21"/>
+      <c r="B15" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="1"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="21"/>
+      <c r="B16" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="1"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="21"/>
+      <c r="B18" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="1"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="21"/>
+      <c r="B19" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="1"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="21"/>
+      <c r="B20" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="H13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="1"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="H14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="1"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="B15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="H15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="1"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="H16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="1"/>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="H17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="1"/>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="H18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="1"/>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="H19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="1"/>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="B20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="H20" s="5"/>
-      <c r="K20" s="5"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="K20" s="3"/>
       <c r="L20" s="1"/>
     </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="21"/>
+      <c r="B21" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="21"/>
+      <c r="B22" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="21"/>
+      <c r="B23" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="21"/>
+      <c r="B24" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="21"/>
+      <c r="B25" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+    </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="B14:I14"/>
+    <mergeCell ref="B15:I15"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="B18:I18"/>
+  </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
